--- a/data/dividends_info_20260529.xlsx
+++ b/data/dividends_info_20260529.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K158"/>
+  <dimension ref="A1:K168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>60.47000122070312</v>
+        <v>58.95000076293945</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1488341296232464</v>
+        <v>0.1526717537492908</v>
       </c>
       <c r="J2" t="n">
         <v>290</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>54.29999923706055</v>
+        <v>54.70000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.289134456418628</v>
+        <v>1.279707477580634</v>
       </c>
       <c r="J3" t="n">
         <v>269</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.140000343322754</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6564551175737441</v>
+        <v>0.6521739265643809</v>
       </c>
       <c r="J4" t="n">
         <v>199</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>60.45999908447266</v>
+        <v>58.95000076293945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1488587518406261</v>
+        <v>0.1526717537492908</v>
       </c>
       <c r="J6" t="n">
         <v>199</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.44499969482422</v>
+        <v>22.53000068664551</v>
       </c>
       <c r="I8" t="n">
-        <v>1.202940537630132</v>
+        <v>1.198402093969045</v>
       </c>
       <c r="J8" t="n">
         <v>178</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.630000114440918</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I9" t="n">
-        <v>3.552397796351747</v>
+        <v>3.533568999855095</v>
       </c>
       <c r="J9" t="n">
         <v>171</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>7.150000095367432</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8391608279680262</v>
       </c>
       <c r="J10" t="n">
         <v>143</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.460000038146973</v>
+        <v>5.119999885559082</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9157509093529076</v>
+        <v>0.9765625218278734</v>
       </c>
       <c r="J12" t="n">
         <v>129</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.44499969482422</v>
+        <v>22.53000068664551</v>
       </c>
       <c r="I14" t="n">
-        <v>1.202940537630132</v>
+        <v>1.198402093969045</v>
       </c>
       <c r="J14" t="n">
         <v>115</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>60.45999908447266</v>
+        <v>58.95000076293945</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1488587518406261</v>
+        <v>0.1526717537492908</v>
       </c>
       <c r="J15" t="n">
         <v>115</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.980000019073486</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="I16" t="n">
-        <v>5.016722392025687</v>
+        <v>5.244755437131728</v>
       </c>
       <c r="J16" t="n">
         <v>108</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.949999809265137</v>
+        <v>5.880000114440918</v>
       </c>
       <c r="I19" t="n">
-        <v>4.201680806959162</v>
+        <v>4.251700597522361</v>
       </c>
       <c r="J19" t="n">
         <v>59</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.559999942779541</v>
+        <v>4.599999904632568</v>
       </c>
       <c r="I20" t="n">
-        <v>3.070175477122116</v>
+        <v>3.043478323967111</v>
       </c>
       <c r="J20" t="n">
         <v>52</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.663000106811523</v>
+        <v>9.625</v>
       </c>
       <c r="I21" t="n">
-        <v>2.690675743827468</v>
+        <v>2.701298701298701</v>
       </c>
       <c r="J21" t="n">
         <v>52</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>15.10000038146973</v>
+        <v>15.47999954223633</v>
       </c>
       <c r="I22" t="n">
-        <v>3.97350983339247</v>
+        <v>3.875969106865494</v>
       </c>
       <c r="J22" t="n">
         <v>52</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.753999948501587</v>
+        <v>3.757999897003174</v>
       </c>
       <c r="I23" t="n">
-        <v>5.860415637134285</v>
+        <v>5.854177914572045</v>
       </c>
       <c r="J23" t="n">
         <v>52</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.369999885559082</v>
+        <v>6.309999942779541</v>
       </c>
       <c r="I25" t="n">
-        <v>3.76766097820637</v>
+        <v>3.803486563809389</v>
       </c>
       <c r="J25" t="n">
         <v>52</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18.64999961853027</v>
+        <v>18.35000038146973</v>
       </c>
       <c r="I26" t="n">
-        <v>2.016085832122022</v>
+        <v>2.049046278929203</v>
       </c>
       <c r="J26" t="n">
         <v>52</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.295000076293945</v>
+        <v>4.289999961853027</v>
       </c>
       <c r="I27" t="n">
-        <v>2.79394639972964</v>
+        <v>2.797202822075715</v>
       </c>
       <c r="J27" t="n">
         <v>45</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.640000104904175</v>
+        <v>2.579999923706055</v>
       </c>
       <c r="I29" t="n">
-        <v>5.681817956043021</v>
+        <v>5.813953660298242</v>
       </c>
       <c r="J29" t="n">
         <v>45</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.220000028610229</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I30" t="n">
-        <v>3.828828779484834</v>
+        <v>3.899082449407415</v>
       </c>
       <c r="J30" t="n">
         <v>38</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.510000228881836</v>
+        <v>4.480000019073486</v>
       </c>
       <c r="I31" t="n">
-        <v>1.552106351386042</v>
+        <v>1.562499993347696</v>
       </c>
       <c r="J31" t="n">
         <v>38</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>31.5</v>
+        <v>31.35000038146973</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.478468893699477</v>
       </c>
       <c r="J32" t="n">
         <v>38</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22.95999908447266</v>
+        <v>22.76000022888184</v>
       </c>
       <c r="I34" t="n">
-        <v>4.137630827008456</v>
+        <v>4.173989413209562</v>
       </c>
       <c r="J34" t="n">
         <v>24</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>30.20000076293945</v>
+        <v>31.14999961853027</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6456953479262764</v>
+        <v>0.6260032179390458</v>
       </c>
       <c r="J35" t="n">
         <v>24</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.889999985694885</v>
+        <v>1.899999976158142</v>
       </c>
       <c r="I36" t="n">
-        <v>1.746031759247188</v>
+        <v>1.736842127057654</v>
       </c>
       <c r="J36" t="n">
         <v>24</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.420000076293945</v>
+        <v>5.394999980926514</v>
       </c>
       <c r="I37" t="n">
-        <v>5.350553430218666</v>
+        <v>5.375347563026249</v>
       </c>
       <c r="J37" t="n">
         <v>24</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.861999988555908</v>
+        <v>3.855999946594238</v>
       </c>
       <c r="I38" t="n">
-        <v>4.14293113604663</v>
+        <v>4.149377650830051</v>
       </c>
       <c r="J38" t="n">
         <v>24</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.717999935150146</v>
+        <v>2.680000066757202</v>
       </c>
       <c r="I39" t="n">
-        <v>5.099337870011521</v>
+        <v>5.171641662222266</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>54.31999969482422</v>
+        <v>54.41999816894531</v>
       </c>
       <c r="I40" t="n">
-        <v>1.15979382094884</v>
+        <v>1.157662662986837</v>
       </c>
       <c r="J40" t="n">
         <v>24</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5.644999980926514</v>
+        <v>5.599999904632568</v>
       </c>
       <c r="I41" t="n">
-        <v>2.480070867547139</v>
+        <v>2.500000042574747</v>
       </c>
       <c r="J41" t="n">
         <v>24</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>19.89999961853027</v>
+        <v>19.95000076293945</v>
       </c>
       <c r="I42" t="n">
-        <v>3.91959806508583</v>
+        <v>3.909774286570374</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>25.31999969482422</v>
+        <v>25.36000061035156</v>
       </c>
       <c r="I43" t="n">
-        <v>3.357030056259252</v>
+        <v>3.351734935105021</v>
       </c>
       <c r="J43" t="n">
         <v>24</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>60.45999908447266</v>
+        <v>58.95000076293945</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1488587518406261</v>
+        <v>0.1526717537492908</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.419999957084656</v>
+        <v>1.429999947547913</v>
       </c>
       <c r="I45" t="n">
-        <v>0.704225373395827</v>
+        <v>0.699300724950897</v>
       </c>
       <c r="J45" t="n">
         <v>24</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.242000102996826</v>
+        <v>6.265999794006348</v>
       </c>
       <c r="I46" t="n">
-        <v>2.904517734835612</v>
+        <v>2.893393009259591</v>
       </c>
       <c r="J46" t="n">
         <v>24</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8.979999542236328</v>
+        <v>8.970000267028809</v>
       </c>
       <c r="I47" t="n">
-        <v>2.895323087458099</v>
+        <v>2.898550638350443</v>
       </c>
       <c r="J47" t="n">
         <v>24</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9.899999618530273</v>
+        <v>9.85200023651123</v>
       </c>
       <c r="I48" t="n">
-        <v>2.797979905792387</v>
+        <v>2.811611787964093</v>
       </c>
       <c r="J48" t="n">
         <v>24</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.039999961853027</v>
+        <v>1.059999942779541</v>
       </c>
       <c r="I49" t="n">
-        <v>1.298076970690103</v>
+        <v>1.273584974410487</v>
       </c>
       <c r="J49" t="n">
         <v>17</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.043999910354614</v>
+        <v>3.068000078201294</v>
       </c>
       <c r="I50" t="n">
-        <v>3.613666335068499</v>
+        <v>3.585397561804847</v>
       </c>
       <c r="J50" t="n">
         <v>17</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.289999961853027</v>
+        <v>3.210000038146973</v>
       </c>
       <c r="I52" t="n">
-        <v>4.863221940886685</v>
+        <v>4.984423616778607</v>
       </c>
       <c r="J52" t="n">
         <v>10</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.8899999856948853</v>
       </c>
       <c r="I53" t="n">
-        <v>2.87356320264113</v>
+        <v>2.808988809194278</v>
       </c>
       <c r="J53" t="n">
         <v>10</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>29.39999961853027</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="I54" t="n">
-        <v>3.775510253069486</v>
+        <v>3.788396003082485</v>
       </c>
       <c r="J54" t="n">
         <v>6</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.9029999971389771</v>
       </c>
       <c r="I55" t="n">
-        <v>3.333333421636513</v>
+        <v>3.322259146738714</v>
       </c>
       <c r="J55" t="n">
         <v>3</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>20.60000038146973</v>
+        <v>20.5</v>
       </c>
       <c r="I57" t="n">
-        <v>2.912621305287531</v>
+        <v>2.926829268292683</v>
       </c>
       <c r="J57" t="n">
         <v>3</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.020000457763672</v>
+        <v>9.079999923706055</v>
       </c>
       <c r="I58" t="n">
-        <v>2.217294787694346</v>
+        <v>2.202643190313694</v>
       </c>
       <c r="J58" t="n">
         <v>3</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.375</v>
+        <v>2.345000028610229</v>
       </c>
       <c r="I59" t="n">
-        <v>7.578947368421051</v>
+        <v>7.675906089718791</v>
       </c>
       <c r="J59" t="n">
         <v>-4</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>15.73999977111816</v>
+        <v>15.94999980926514</v>
       </c>
       <c r="I61" t="n">
-        <v>1.588310061215713</v>
+        <v>1.567398137865672</v>
       </c>
       <c r="J61" t="n">
         <v>-4</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.640000104904175</v>
+        <v>3.829999923706055</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8241758004232191</v>
+        <v>0.7832898328355801</v>
       </c>
       <c r="J62" t="n">
         <v>-4</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>3.950000047683716</v>
+        <v>4.039999961853027</v>
       </c>
       <c r="I63" t="n">
-        <v>3.797468308588</v>
+        <v>3.712871322186832</v>
       </c>
       <c r="J63" t="n">
         <v>-4</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>13.10000038146973</v>
+        <v>13.05000019073486</v>
       </c>
       <c r="I64" t="n">
-        <v>4.427480787103062</v>
+        <v>4.444444379485786</v>
       </c>
       <c r="J64" t="n">
         <v>-4</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.272000074386597</v>
+        <v>2.249000072479248</v>
       </c>
       <c r="I65" t="n">
-        <v>4.57746463886355</v>
+        <v>4.624277307619323</v>
       </c>
       <c r="J65" t="n">
         <v>-11</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>11.07499980926514</v>
+        <v>10.77999973297119</v>
       </c>
       <c r="I66" t="n">
-        <v>2.618510203109813</v>
+        <v>2.690167042518747</v>
       </c>
       <c r="J66" t="n">
         <v>-11</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>38.45000076293945</v>
+        <v>38.70999908447266</v>
       </c>
       <c r="I68" t="n">
-        <v>4.265279499241871</v>
+        <v>4.236631461605579</v>
       </c>
       <c r="J68" t="n">
         <v>-11</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>34.77000045776367</v>
+        <v>34.84999847412109</v>
       </c>
       <c r="I69" t="n">
-        <v>5.752085055130987</v>
+        <v>5.738881169493191</v>
       </c>
       <c r="J69" t="n">
         <v>-11</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.329999923706055</v>
+        <v>3.322000026702881</v>
       </c>
       <c r="I70" t="n">
-        <v>3.003003071805091</v>
+        <v>3.010234774117417</v>
       </c>
       <c r="J70" t="n">
         <v>-11</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>42.9900016784668</v>
+        <v>43.06999969482422</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3453361111971343</v>
+        <v>0.3446946855164261</v>
       </c>
       <c r="J71" t="n">
         <v>-11</v>
@@ -3781,11 +3781,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2.06</v>
+        <v>0.92</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3809,14 +3809,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>IT0001128047</t>
+          <t>IT0003188064</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>89</v>
+        <v>20.28000068664551</v>
       </c>
       <c r="I72" t="n">
-        <v>2.314606741573034</v>
+        <v>4.536488998276145</v>
       </c>
       <c r="J72" t="n">
         <v>-11</v>
@@ -3828,11 +3828,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>IT0003121677</t>
+          <t>NL0015001KT6</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>15.47000026702881</v>
+        <v>11.67000007629395</v>
       </c>
       <c r="I73" t="n">
-        <v>4.848092999703911</v>
+        <v>2.570694070597396</v>
       </c>
       <c r="J73" t="n">
         <v>-11</v>
@@ -3875,11 +3875,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.3</v>
+        <v>1.04</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3903,14 +3903,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>NL0013995087</t>
+          <t>IT0004764699</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>14.67000007629395</v>
+        <v>82.48000335693359</v>
       </c>
       <c r="I74" t="n">
-        <v>2.044989764415792</v>
+        <v>1.260911684859399</v>
       </c>
       <c r="J74" t="n">
         <v>-11</v>
@@ -3922,11 +3922,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3950,14 +3950,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>IT0005246191</t>
+          <t>IT0001347308</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>52.40000152587891</v>
+        <v>46.5</v>
       </c>
       <c r="I75" t="n">
-        <v>1.622137357343794</v>
+        <v>1.505376344086022</v>
       </c>
       <c r="J75" t="n">
         <v>-11</v>
@@ -3969,11 +3969,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.85</v>
+        <v>2.2</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3992,19 +3992,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>IT0003115950</t>
+          <t>IT0001031084</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>35.59999847412109</v>
+        <v>54.70000076293945</v>
       </c>
       <c r="I76" t="n">
-        <v>2.387640551776695</v>
+        <v>4.021937786681993</v>
       </c>
       <c r="J76" t="n">
         <v>-11</v>
@@ -4016,11 +4016,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1.3</v>
+        <v>0.86</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4044,14 +4044,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>IT0003492391</t>
+          <t>IT0005508921</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>67.87999725341797</v>
+        <v>9.227999687194824</v>
       </c>
       <c r="I77" t="n">
-        <v>1.915144449913102</v>
+        <v>9.319462821323819</v>
       </c>
       <c r="J77" t="n">
         <v>-11</v>
@@ -4063,11 +4063,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4091,14 +4091,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>IT0001463063</t>
+          <t>IT0000066123</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>7.179999828338623</v>
+        <v>11.61800003051758</v>
       </c>
       <c r="I78" t="n">
-        <v>8.356546160793345</v>
+        <v>4.820106718273543</v>
       </c>
       <c r="J78" t="n">
         <v>-11</v>
@@ -4110,11 +4110,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.47</v>
+        <v>0.04</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4138,14 +4138,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>IT0005669558</t>
+          <t>IT0001472171</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>7.099999904632568</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I79" t="n">
-        <v>6.619718398775428</v>
+        <v>1.834862329132901</v>
       </c>
       <c r="J79" t="n">
         <v>-11</v>
@@ -4157,11 +4157,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4180,19 +4180,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>IT0005312027</t>
+          <t>IT0003127930</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>5.630000114440918</v>
+        <v>9.289999961853027</v>
       </c>
       <c r="I80" t="n">
-        <v>3.552397796351747</v>
+        <v>3.229278807662778</v>
       </c>
       <c r="J80" t="n">
         <v>-11</v>
@@ -4204,11 +4204,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>0.108</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4232,14 +4232,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>IT0001157020</t>
+          <t>IT0005244618</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>23.23999977111816</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I81" t="n">
-        <v>4.302926032050844</v>
+        <v>4.909090802689231</v>
       </c>
       <c r="J81" t="n">
         <v>-11</v>
@@ -4251,11 +4251,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.215</v>
+        <v>2.06</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4279,14 +4279,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>IT0004356751</t>
+          <t>IT0001128047</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>4.659999847412109</v>
+        <v>89.40000152587891</v>
       </c>
       <c r="I82" t="n">
-        <v>4.613734056652349</v>
+        <v>2.304250519955176</v>
       </c>
       <c r="J82" t="n">
         <v>-11</v>
@@ -4298,11 +4298,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.27</v>
+        <v>0.75</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4321,19 +4321,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>IT0003132476</t>
+          <t>IT0003121677</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>22.44499969482422</v>
+        <v>15.39999961853027</v>
       </c>
       <c r="I83" t="n">
-        <v>1.202940537630132</v>
+        <v>4.870129990766698</v>
       </c>
       <c r="J83" t="n">
         <v>-11</v>
@@ -4345,11 +4345,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4373,14 +4373,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>IT0005521247</t>
+          <t>NL0013995087</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>10</v>
+        <v>14.5600004196167</v>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>2.060439501058048</v>
       </c>
       <c r="J84" t="n">
         <v>-11</v>
@@ -4392,11 +4392,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.24</v>
+        <v>0.85</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4420,14 +4420,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>IT0004967292</t>
+          <t>IT0005246191</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>8.939999580383301</v>
+        <v>52</v>
       </c>
       <c r="I85" t="n">
-        <v>2.684563884394612</v>
+        <v>1.634615384615385</v>
       </c>
       <c r="J85" t="n">
         <v>-11</v>
@@ -4439,11 +4439,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4467,14 +4467,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>IT0000072170</t>
+          <t>IT0003115950</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>20.80999946594238</v>
+        <v>35.68000030517578</v>
       </c>
       <c r="I86" t="n">
-        <v>3.796251899443404</v>
+        <v>2.382286975139678</v>
       </c>
       <c r="J86" t="n">
         <v>-11</v>
@@ -4486,11 +4486,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.093</v>
+        <v>1.3</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4514,14 +4514,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>IT0005345233</t>
+          <t>IT0003492391</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5.28000020980835</v>
+        <v>66.51999664306641</v>
       </c>
       <c r="I87" t="n">
-        <v>1.761363566373337</v>
+        <v>1.954299557433161</v>
       </c>
       <c r="J87" t="n">
         <v>-11</v>
@@ -4533,11 +4533,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.06</v>
+        <v>0.6</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4556,19 +4556,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>IT0005359101</t>
+          <t>IT0001463063</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>7</v>
+        <v>7.079999923706055</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8571428571428572</v>
+        <v>8.474576362508314</v>
       </c>
       <c r="J88" t="n">
         <v>-11</v>
@@ -4580,11 +4580,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4608,14 +4608,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>IT0001078911</t>
+          <t>IT0005669558</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>36.20000076293945</v>
+        <v>7.050000190734863</v>
       </c>
       <c r="I89" t="n">
-        <v>0.9668508083522478</v>
+        <v>6.666666486302734</v>
       </c>
       <c r="J89" t="n">
         <v>-11</v>
@@ -4627,11 +4627,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5543</v>
+        <v>0.2</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4650,19 +4650,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>IT0005090300</t>
+          <t>IT0005312027</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>6.820000171661377</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I90" t="n">
-        <v>8.127565777831505</v>
+        <v>3.533568999855095</v>
       </c>
       <c r="J90" t="n">
         <v>-11</v>
@@ -4674,11 +4674,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4702,14 +4702,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>IT0001077780</t>
+          <t>IT0001157020</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>2.279999971389771</v>
+        <v>22.94000053405762</v>
       </c>
       <c r="I91" t="n">
-        <v>2.631578980390385</v>
+        <v>4.35919780610014</v>
       </c>
       <c r="J91" t="n">
         <v>-11</v>
@@ -4721,11 +4721,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.2</v>
+        <v>0.215</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4749,14 +4749,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>IT0003411417</t>
+          <t>IT0004356751</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>12.85000038146973</v>
+        <v>4.800000190734863</v>
       </c>
       <c r="I92" t="n">
-        <v>1.556420187258585</v>
+        <v>4.479166488680582</v>
       </c>
       <c r="J92" t="n">
         <v>-11</v>
@@ -4768,11 +4768,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.103</v>
+        <v>0.27</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4791,19 +4791,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>IT0005186371</t>
+          <t>IT0003132476</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>7.650000095367432</v>
+        <v>22.53000068664551</v>
       </c>
       <c r="I93" t="n">
-        <v>1.346405211973437</v>
+        <v>1.198402093969045</v>
       </c>
       <c r="J93" t="n">
         <v>-11</v>
@@ -4815,11 +4815,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4843,14 +4843,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>IT0000072618</t>
+          <t>IT0005521247</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>5.803999900817871</v>
+        <v>9.699999809265137</v>
       </c>
       <c r="I94" t="n">
-        <v>3.273604466692464</v>
+        <v>2.061855710646161</v>
       </c>
       <c r="J94" t="n">
         <v>-11</v>
@@ -4862,11 +4862,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.432</v>
+        <v>0.24</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>IT0005211237</t>
+          <t>IT0004967292</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>10.07999992370605</v>
+        <v>8.854999542236328</v>
       </c>
       <c r="I95" t="n">
-        <v>4.285714318152188</v>
+        <v>2.710333285227794</v>
       </c>
       <c r="J95" t="n">
         <v>-11</v>
@@ -4909,11 +4909,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.44</v>
+        <v>0.79</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4937,14 +4937,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>IT0005541336</t>
+          <t>IT0000072170</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>25.36000061035156</v>
+        <v>20.95999908447266</v>
       </c>
       <c r="I96" t="n">
-        <v>1.735015731113188</v>
+        <v>3.769084134098263</v>
       </c>
       <c r="J96" t="n">
         <v>-11</v>
@@ -4956,11 +4956,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.03</v>
+        <v>0.093</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4984,14 +4984,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>IT0004522162</t>
+          <t>IT0005345233</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1.039999961853027</v>
+        <v>5.320000171661377</v>
       </c>
       <c r="I97" t="n">
-        <v>2.88461549042245</v>
+        <v>1.748120244344976</v>
       </c>
       <c r="J97" t="n">
         <v>-11</v>
@@ -5003,11 +5003,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.47</v>
+        <v>0.06</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5026,19 +5026,19 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>IT0003428445</t>
+          <t>IT0005359101</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>7.110000133514404</v>
+        <v>7.150000095367432</v>
       </c>
       <c r="I98" t="n">
-        <v>6.610407752097798</v>
+        <v>0.8391608279680262</v>
       </c>
       <c r="J98" t="n">
         <v>-11</v>
@@ -5050,11 +5050,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1.4</v>
+        <v>0.35</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5078,14 +5078,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>IT0004965148</t>
+          <t>IT0001078911</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>56.54000091552734</v>
+        <v>35.88000106811523</v>
       </c>
       <c r="I99" t="n">
-        <v>2.47612305859642</v>
+        <v>0.9754737725217837</v>
       </c>
       <c r="J99" t="n">
         <v>-11</v>
@@ -5097,11 +5097,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.3</v>
+        <v>0.5543</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5125,14 +5125,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>IT0005366767</t>
+          <t>IT0005090300</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>3.519999980926514</v>
+        <v>6.679999828338623</v>
       </c>
       <c r="I100" t="n">
-        <v>8.522727318908558</v>
+        <v>8.297904404854744</v>
       </c>
       <c r="J100" t="n">
         <v>-11</v>
@@ -5144,11 +5144,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>IT0005594418</t>
+          <t>IT0001077780</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>16.20000076293945</v>
+        <v>2.289999961853027</v>
       </c>
       <c r="I101" t="n">
-        <v>0.7407407058555365</v>
+        <v>2.620087379890132</v>
       </c>
       <c r="J101" t="n">
         <v>-11</v>
@@ -5191,11 +5191,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -5219,14 +5219,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>IT0005453748</t>
+          <t>IT0003411417</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>3.240000009536743</v>
+        <v>12.89999961853027</v>
       </c>
       <c r="I102" t="n">
-        <v>5.246913564802943</v>
+        <v>1.550387642746198</v>
       </c>
       <c r="J102" t="n">
         <v>-11</v>
@@ -5238,11 +5238,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7</v>
+        <v>0.103</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5266,14 +5266,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>IT0005373789</t>
+          <t>IT0005186371</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>22.60000038146973</v>
+        <v>7.550000190734863</v>
       </c>
       <c r="I103" t="n">
-        <v>3.097345080462682</v>
+        <v>1.364238376131415</v>
       </c>
       <c r="J103" t="n">
         <v>-11</v>
@@ -5285,11 +5285,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.035</v>
+        <v>0.19</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5313,14 +5313,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>IT0005378143</t>
+          <t>IT0000072618</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>2.359999895095825</v>
+        <v>5.807000160217285</v>
       </c>
       <c r="I104" t="n">
-        <v>1.483050913380607</v>
+        <v>3.271913117923706</v>
       </c>
       <c r="J104" t="n">
         <v>-11</v>
@@ -5332,11 +5332,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.33</v>
+        <v>0.432</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5360,14 +5360,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>IT0005054967</t>
+          <t>IT0005211237</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>5.630000114440918</v>
+        <v>10.0649995803833</v>
       </c>
       <c r="I105" t="n">
-        <v>5.861456363980383</v>
+        <v>4.292101520222302</v>
       </c>
       <c r="J105" t="n">
         <v>-11</v>
@@ -5379,11 +5379,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5407,14 +5407,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>IT0004931496</t>
+          <t>IT0005541336</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>0.9020000100135803</v>
+        <v>25.42000007629395</v>
       </c>
       <c r="I106" t="n">
-        <v>7.760532064622272</v>
+        <v>1.730920529816729</v>
       </c>
       <c r="J106" t="n">
         <v>-11</v>
@@ -5426,11 +5426,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.71</v>
+        <v>0.03</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5454,14 +5454,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>IT0003828271</t>
+          <t>IT0004522162</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>51.25</v>
+        <v>1.039999961853027</v>
       </c>
       <c r="I107" t="n">
-        <v>1.385365853658537</v>
+        <v>2.88461549042245</v>
       </c>
       <c r="J107" t="n">
         <v>-11</v>
@@ -5473,11 +5473,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1.35</v>
+        <v>0.47</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>IT0005282865</t>
+          <t>IT0003428445</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>103</v>
+        <v>7.070000171661377</v>
       </c>
       <c r="I108" t="n">
-        <v>1.310679611650486</v>
+        <v>6.647807476496211</v>
       </c>
       <c r="J108" t="n">
         <v>-11</v>
@@ -5520,11 +5520,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.08</v>
+        <v>1.4</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5548,14 +5548,14 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>IT0005543613</t>
+          <t>IT0004965148</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>7.28000020980835</v>
+        <v>55.86000061035156</v>
       </c>
       <c r="I109" t="n">
-        <v>1.098901067230959</v>
+        <v>2.506265636775812</v>
       </c>
       <c r="J109" t="n">
         <v>-11</v>
@@ -5567,11 +5567,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5595,14 +5595,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>IT0001017851</t>
+          <t>IT0005366767</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>264</v>
+        <v>3.509999990463257</v>
       </c>
       <c r="I110" t="n">
-        <v>1.136363636363636</v>
+        <v>8.547008570230947</v>
       </c>
       <c r="J110" t="n">
         <v>-11</v>
@@ -5614,11 +5614,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5642,14 +5642,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>IT0005495657</t>
+          <t>IT0005594418</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>4.151000022888184</v>
+        <v>16.10000038146973</v>
       </c>
       <c r="I111" t="n">
-        <v>4.095398676527044</v>
+        <v>0.7453415972468785</v>
       </c>
       <c r="J111" t="n">
         <v>-11</v>
@@ -5661,11 +5661,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.297</v>
+        <v>0.17</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5689,14 +5689,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>IT0005568461</t>
+          <t>IT0005453748</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>6.949999809265137</v>
+        <v>3.299999952316284</v>
       </c>
       <c r="I112" t="n">
-        <v>4.273381412242132</v>
+        <v>5.151515225952543</v>
       </c>
       <c r="J112" t="n">
         <v>-11</v>
@@ -5708,11 +5708,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>IT0001206769</t>
+          <t>IT0005373789</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>57.20000076293945</v>
+        <v>23.29999923706055</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7867132762200246</v>
+        <v>3.004291943866646</v>
       </c>
       <c r="J113" t="n">
         <v>-11</v>
@@ -5755,11 +5755,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5783,14 +5783,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>IT0005595423</t>
+          <t>IT0005378143</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>5.800000190734863</v>
+        <v>2.420000076293945</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6896551497342619</v>
+        <v>1.446280946139471</v>
       </c>
       <c r="J114" t="n">
         <v>-11</v>
@@ -5802,11 +5802,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1.05</v>
+        <v>0.33</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5830,14 +5830,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>IT0003549422</t>
+          <t>IT0005054967</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>37.81999969482422</v>
+        <v>5.650000095367432</v>
       </c>
       <c r="I115" t="n">
-        <v>2.776308853708679</v>
+        <v>5.840707866015344</v>
       </c>
       <c r="J115" t="n">
         <v>-11</v>
@@ -5849,11 +5849,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5877,14 +5877,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>IT0005621070</t>
+          <t>IT0004931496</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1.5</v>
+        <v>0.9210000038146973</v>
       </c>
       <c r="I116" t="n">
-        <v>3.333333333333333</v>
+        <v>7.600434279051732</v>
       </c>
       <c r="J116" t="n">
         <v>-11</v>
@@ -5896,11 +5896,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.38</v>
+        <v>0.71</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -5924,14 +5924,14 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>IT0005162406</t>
+          <t>IT0003828271</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>17.69000053405762</v>
+        <v>51.5</v>
       </c>
       <c r="I117" t="n">
-        <v>2.148106209880583</v>
+        <v>1.378640776699029</v>
       </c>
       <c r="J117" t="n">
         <v>-11</v>
@@ -5943,15 +5943,15 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6</v>
+        <v>1.35</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5971,14 +5971,14 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>LU2598331598</t>
+          <t>IT0005282865</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>25.81999969482422</v>
+        <v>102.9000015258789</v>
       </c>
       <c r="I118" t="n">
-        <v>2.323780042957451</v>
+        <v>1.311953333315045</v>
       </c>
       <c r="J118" t="n">
         <v>-11</v>
@@ -5990,11 +5990,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.35</v>
+        <v>0.08</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6018,14 +6018,14 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>IT0001454435</t>
+          <t>IT0005543613</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>35.79999923706055</v>
+        <v>7.239999771118164</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9776536521198476</v>
+        <v>1.104972410622668</v>
       </c>
       <c r="J119" t="n">
         <v>-11</v>
@@ -6037,11 +6037,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.017</v>
+        <v>3</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6065,14 +6065,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>IT0005658841</t>
+          <t>IT0001017851</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>3.160000085830688</v>
+        <v>264</v>
       </c>
       <c r="I120" t="n">
-        <v>0.5379746689320455</v>
+        <v>1.136363636363636</v>
       </c>
       <c r="J120" t="n">
         <v>-11</v>
@@ -6084,11 +6084,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.01</v>
+        <v>0.17</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -6112,14 +6112,14 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>IT0005573065</t>
+          <t>IT0005495657</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>2.890000104904175</v>
+        <v>4.119999885559082</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3460207486854598</v>
+        <v>4.126213706846526</v>
       </c>
       <c r="J121" t="n">
         <v>-11</v>
@@ -6131,11 +6131,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1.12</v>
+        <v>0.297</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6159,14 +6159,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>IT0004810054</t>
+          <t>IT0005568461</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>21.17000007629395</v>
+        <v>7.099999904632568</v>
       </c>
       <c r="I122" t="n">
-        <v>5.290505413149101</v>
+        <v>4.183098647736813</v>
       </c>
       <c r="J122" t="n">
         <v>-11</v>
@@ -6178,11 +6178,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6206,14 +6206,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>IT0004717200</t>
+          <t>IT0001206769</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>1.350000023841858</v>
+        <v>56.5</v>
       </c>
       <c r="I123" t="n">
-        <v>7.407407276587888</v>
+        <v>0.7964601769911505</v>
       </c>
       <c r="J123" t="n">
         <v>-11</v>
@@ -6225,11 +6225,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6253,14 +6253,14 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>IT0003865588</t>
+          <t>IT0005595423</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>9.260000228881836</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I124" t="n">
-        <v>2.807775308569248</v>
+        <v>0.7017544094471985</v>
       </c>
       <c r="J124" t="n">
         <v>-11</v>
@@ -6272,11 +6272,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.09229999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -6300,14 +6300,14 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>IT0005610958</t>
+          <t>IT0003549422</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>2.28600001335144</v>
+        <v>37.11999893188477</v>
       </c>
       <c r="I125" t="n">
-        <v>4.037620273880995</v>
+        <v>2.828663874497279</v>
       </c>
       <c r="J125" t="n">
         <v>-11</v>
@@ -6319,11 +6319,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -6332,12 +6332,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6347,30 +6347,30 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>IT0001006128</t>
+          <t>IT0005621070</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>9.140000343322754</v>
+        <v>1.5</v>
       </c>
       <c r="I126" t="n">
-        <v>3.829321519180174</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J126" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K126" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.096</v>
+        <v>0.38</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -6379,12 +6379,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6394,44 +6394,44 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>IT0005543332</t>
+          <t>IT0005162406</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>5.199999809265137</v>
+        <v>17.80999946594238</v>
       </c>
       <c r="I127" t="n">
-        <v>1.846153913870368</v>
+        <v>2.133632854547046</v>
       </c>
       <c r="J127" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K127" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6441,30 +6441,30 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>IT0005416281</t>
+          <t>LU2598331598</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>6.25</v>
+        <v>26.09000015258789</v>
       </c>
       <c r="I128" t="n">
-        <v>4.8</v>
+        <v>2.299731684518543</v>
       </c>
       <c r="J128" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K128" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -6473,12 +6473,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6488,30 +6488,30 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>IT0005037905</t>
+          <t>IT0001454435</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>11.69999980926514</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="I129" t="n">
-        <v>1.70940173726859</v>
+        <v>0.9615384212310112</v>
       </c>
       <c r="J129" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K129" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.06</v>
+        <v>0.017</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -6520,45 +6520,45 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>IT0005337818</t>
+          <t>IT0005658841</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>9.140000343322754</v>
+        <v>3.160000085830688</v>
       </c>
       <c r="I130" t="n">
-        <v>0.6564551175737441</v>
+        <v>0.5379746689320455</v>
       </c>
       <c r="J130" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K130" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -6567,12 +6567,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6582,30 +6582,30 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>IT0005075764</t>
+          <t>IT0005573065</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>18.86000061035156</v>
+        <v>2.845000028610229</v>
       </c>
       <c r="I131" t="n">
-        <v>2.651113381860488</v>
+        <v>0.3514938453229105</v>
       </c>
       <c r="J131" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K131" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.06</v>
+        <v>1.12</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6629,30 +6629,30 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>IT0004376858</t>
+          <t>IT0004810054</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>2.220000028610229</v>
+        <v>21.23999977111816</v>
       </c>
       <c r="I132" t="n">
-        <v>2.702702667871647</v>
+        <v>5.27306973667184</v>
       </c>
       <c r="J132" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K132" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -6661,12 +6661,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6676,30 +6676,30 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>IT0005138703</t>
+          <t>IT0004717200</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>15.60000038146973</v>
+        <v>1.389999985694885</v>
       </c>
       <c r="I133" t="n">
-        <v>3.205128126752606</v>
+        <v>7.194244678355753</v>
       </c>
       <c r="J133" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K133" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -6708,12 +6708,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6723,30 +6723,30 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>IT0005430951</t>
+          <t>IT0003865588</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>3.660000085830688</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="I134" t="n">
-        <v>2.73224037308468</v>
+        <v>2.813852883554092</v>
       </c>
       <c r="J134" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K134" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.11</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6770,30 +6770,30 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>IT0005339160</t>
+          <t>IT0005610958</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>3.299999952316284</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I135" t="n">
-        <v>3.333333381498703</v>
+        <v>4.120535696742638</v>
       </c>
       <c r="J135" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="K135" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -6817,14 +6817,14 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>IT0005545238</t>
+          <t>IT0001006128</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>8.899999618530273</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I136" t="n">
-        <v>0.9550562207106782</v>
+        <v>3.804347904958889</v>
       </c>
       <c r="J136" t="n">
         <v>-18</v>
@@ -6836,11 +6836,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.095</v>
+        <v>0.096</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>IT0005466963</t>
+          <t>IT0005543332</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>4.75</v>
+        <v>5.199999809265137</v>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>1.846153913870368</v>
       </c>
       <c r="J137" t="n">
         <v>-18</v>
@@ -6883,11 +6883,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -6911,14 +6911,14 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>IT0005521551</t>
+          <t>IT0005416281</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>1.269999980926514</v>
+        <v>6.25</v>
       </c>
       <c r="I138" t="n">
-        <v>2.362204759886205</v>
+        <v>4.8</v>
       </c>
       <c r="J138" t="n">
         <v>-18</v>
@@ -6930,11 +6930,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -6958,14 +6958,14 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>IT0005246142</t>
+          <t>IT0005037905</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>7.949999809265137</v>
+        <v>11.39999961853027</v>
       </c>
       <c r="I139" t="n">
-        <v>1.13207549885865</v>
+        <v>1.754386023617996</v>
       </c>
       <c r="J139" t="n">
         <v>-18</v>
@@ -6977,11 +6977,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -7000,19 +7000,19 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>IT0005532525</t>
+          <t>IT0005337818</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>8.399999618530273</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I140" t="n">
-        <v>1.190476244539363</v>
+        <v>0.6521739265643809</v>
       </c>
       <c r="J140" t="n">
         <v>-18</v>
@@ -7024,11 +7024,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7052,14 +7052,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>IT0004171440</t>
+          <t>IT0005075764</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>7.440000057220459</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="I141" t="n">
-        <v>2.956989224569855</v>
+        <v>2.64550269889837</v>
       </c>
       <c r="J141" t="n">
         <v>-18</v>
@@ -7071,11 +7071,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.61</v>
+        <v>0.06</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -7084,12 +7084,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7099,30 +7099,30 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>IT0004720733</t>
+          <t>IT0004376858</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>24.60000038146973</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I142" t="n">
-        <v>2.4796747582959</v>
+        <v>2.702702667871647</v>
       </c>
       <c r="J142" t="n">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="K142" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -7131,12 +7131,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7146,30 +7146,30 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>IT0005386369</t>
+          <t>IT0005138703</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>2.779999971389771</v>
+        <v>15.53999996185303</v>
       </c>
       <c r="I143" t="n">
-        <v>5.395683508766814</v>
+        <v>3.217503225401416</v>
       </c>
       <c r="J143" t="n">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="K143" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7193,30 +7193,30 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>IT0001268561</t>
+          <t>IT0005430951</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>11.5</v>
+        <v>3.660000085830688</v>
       </c>
       <c r="I144" t="n">
-        <v>6.08695652173913</v>
+        <v>2.73224037308468</v>
       </c>
       <c r="J144" t="n">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="K144" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5105</v>
+        <v>0.11</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7240,44 +7240,44 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>IT0001041000</t>
+          <t>IT0005339160</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>9.189999580383301</v>
+        <v>3.170000076293945</v>
       </c>
       <c r="I145" t="n">
-        <v>5.554951287372178</v>
+        <v>3.470031462226375</v>
       </c>
       <c r="J145" t="n">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="K145" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.27</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7287,30 +7287,30 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>LU2592315662</t>
+          <t>IT0005545238</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>7.114999771118164</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I146" t="n">
-        <v>3.794799840978321</v>
+        <v>0.9550562207106782</v>
       </c>
       <c r="J146" t="n">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="K146" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.35</v>
+        <v>0.095</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7334,30 +7334,30 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>IT0003850929</t>
+          <t>IT0005466963</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>6.934999942779541</v>
+        <v>4.820000171661377</v>
       </c>
       <c r="I147" t="n">
-        <v>5.046863776320672</v>
+        <v>1.970954286652131</v>
       </c>
       <c r="J147" t="n">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="K147" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1.1</v>
+        <v>0.03</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -7366,12 +7366,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7381,30 +7381,30 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>IT0005203424</t>
+          <t>IT0005521551</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>42</v>
+        <v>1.25</v>
       </c>
       <c r="I148" t="n">
-        <v>2.619047619047619</v>
+        <v>2.4</v>
       </c>
       <c r="J148" t="n">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="K148" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.75</v>
+        <v>0.09</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -7413,45 +7413,45 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>IT0005252736</t>
+          <t>IT0005246142</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>17.29999923706055</v>
+        <v>7.949999809265137</v>
       </c>
       <c r="I149" t="n">
-        <v>4.335260306794285</v>
+        <v>1.13207549885865</v>
       </c>
       <c r="J149" t="n">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="K149" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.43</v>
+        <v>0.1</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -7460,12 +7460,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7475,30 +7475,30 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>IT0003203947</t>
+          <t>IT0005532525</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>11.25</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="I150" t="n">
-        <v>3.822222222222222</v>
+        <v>1.190476244539363</v>
       </c>
       <c r="J150" t="n">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="K150" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -7507,12 +7507,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7522,30 +7522,30 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>IT0005322612</t>
+          <t>IT0004171440</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>4.59499979019165</v>
+        <v>7.389999866485596</v>
       </c>
       <c r="I151" t="n">
-        <v>3.264417994538009</v>
+        <v>2.976995994245176</v>
       </c>
       <c r="J151" t="n">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="K151" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.197169</v>
+        <v>0.61</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -7569,14 +7569,14 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>IT0005455875</t>
+          <t>IT0004720733</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>12.47999954223633</v>
+        <v>24.39999961853027</v>
       </c>
       <c r="I152" t="n">
-        <v>1.579879865641956</v>
+        <v>2.500000039085013</v>
       </c>
       <c r="J152" t="n">
         <v>-25</v>
@@ -7588,11 +7588,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1.1</v>
+        <v>0.15</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -7616,14 +7616,14 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>IT0005253205</t>
+          <t>IT0005386369</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>28.64999961853027</v>
+        <v>2.819999933242798</v>
       </c>
       <c r="I153" t="n">
-        <v>3.839441586898106</v>
+        <v>5.319149062089187</v>
       </c>
       <c r="J153" t="n">
         <v>-25</v>
@@ -7635,11 +7635,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -7663,14 +7663,14 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>IT0005107492</t>
+          <t>IT0001268561</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>66.69999694824219</v>
+        <v>11.39999961853027</v>
       </c>
       <c r="I154" t="n">
-        <v>0.7046477084020112</v>
+        <v>6.140351082662987</v>
       </c>
       <c r="J154" t="n">
         <v>-25</v>
@@ -7682,11 +7682,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1.2</v>
+        <v>0.5105</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -7710,14 +7710,14 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>IT0005274094</t>
+          <t>IT0001041000</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>90.90000152587891</v>
+        <v>9.260000228881836</v>
       </c>
       <c r="I155" t="n">
-        <v>1.320131991041127</v>
+        <v>5.512958827017695</v>
       </c>
       <c r="J155" t="n">
         <v>-25</v>
@@ -7729,7 +7729,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7757,14 +7757,14 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>IT0005513202</t>
+          <t>LU2592315662</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>23</v>
+        <v>7.005000114440918</v>
       </c>
       <c r="I156" t="n">
-        <v>1.173913043478261</v>
+        <v>3.854389658658117</v>
       </c>
       <c r="J156" t="n">
         <v>-25</v>
@@ -7776,11 +7776,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -7804,14 +7804,14 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>IT0001018362</t>
+          <t>IT0003850929</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>10.35000038146973</v>
+        <v>6.965000152587891</v>
       </c>
       <c r="I157" t="n">
-        <v>3.671497449220761</v>
+        <v>5.025125518051213</v>
       </c>
       <c r="J157" t="n">
         <v>-25</v>
@@ -7823,11 +7823,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -7851,19 +7851,489 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>IT0005440893</t>
+          <t>IT0005203424</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>33.79999923706055</v>
+        <v>42</v>
       </c>
       <c r="I158" t="n">
-        <v>0.887573984531515</v>
+        <v>2.619047619047619</v>
       </c>
       <c r="J158" t="n">
         <v>-25</v>
       </c>
       <c r="K158" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>First Capital S.p.A.</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Straordinario</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>IT0005252736</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>17.14999961853027</v>
+      </c>
+      <c r="I159" t="n">
+        <v>4.373177939838775</v>
+      </c>
+      <c r="J159" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K159" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>GEFRAN S.p.A.</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>IT0003203947</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>11.35000038146973</v>
+      </c>
+      <c r="I160" t="n">
+        <v>3.788546128174832</v>
+      </c>
+      <c r="J160" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K160" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>IGD SIIQ S.p.A.</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>IT0005322612</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>4.550000190734863</v>
+      </c>
+      <c r="I161" t="n">
+        <v>3.296703158506324</v>
+      </c>
+      <c r="J161" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K161" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>INTERCOS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>0.197169</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>IT0005455875</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>12.23999977111816</v>
+      </c>
+      <c r="I162" t="n">
+        <v>1.610857873259486</v>
+      </c>
+      <c r="J162" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K162" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ITALMOBILIARE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>IT0005253205</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>28.45000076293945</v>
+      </c>
+      <c r="I163" t="n">
+        <v>3.866432233748553</v>
+      </c>
+      <c r="J163" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K163" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>LU-VE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>IT0005107492</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>67.69999694824219</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0.6942393222843467</v>
+      </c>
+      <c r="J164" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K164" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Pharmanutra S.p.A.</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>IT0005274094</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>90.59999847412109</v>
+      </c>
+      <c r="I165" t="n">
+        <v>1.324503333565471</v>
+      </c>
+      <c r="J165" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K165" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>REVO Insurance S.p.A.</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>IT0005513202</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>22.85000038146973</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1.181619236290942</v>
+      </c>
+      <c r="J166" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K166" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>VALSOIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>IT0001018362</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>10.44999980926514</v>
+      </c>
+      <c r="I167" t="n">
+        <v>3.636363702735056</v>
+      </c>
+      <c r="J167" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K167" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>WIIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>IT0005440893</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>34.29999923706055</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0.874635587967755</v>
+      </c>
+      <c r="J168" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K168" t="n">
         <v>-23</v>
       </c>
     </row>
@@ -9575,104 +10045,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DBA GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0005285942</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-07-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4.559999942779541</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3.070175477122116</v>
-      </c>
-      <c r="I2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9683,61 +10058,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>OPS Retail S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>